--- a/WebHosting_OnCall_2026.xlsx
+++ b/WebHosting_OnCall_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uhgazure.sharepoint.com/sites/optumrxwebhostingkb/Shared Documents/Team Onboarding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1866479-FE18-42B3-82B2-13EF8F0A800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D15D341-F4BF-4196-9C14-104FE0C09425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="On-Call Schedule" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -189,7 +189,13 @@
     <t>Martin Luther King Jr. Day, January 18th (USA)</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Short Name</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -198,16 +204,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Aarti</t>
-  </si>
-  <si>
-    <t>011-91-9535286278</t>
+    <t>Abhishek Ponneri</t>
+  </si>
+  <si>
+    <t>abhishek_ponneri@optum.com</t>
+  </si>
+  <si>
+    <t>011-91-xxxxxxxx</t>
   </si>
   <si>
     <t>India</t>
   </si>
   <si>
-    <t>Avinash</t>
+    <t>Avinash Kumar</t>
+  </si>
+  <si>
+    <t>Avinash.Kumar@optum.com</t>
   </si>
   <si>
     <t>630-352-6496</t>
@@ -216,52 +228,136 @@
     <t>USA</t>
   </si>
   <si>
+    <t>Deepak Gilkarwar</t>
+  </si>
+  <si>
+    <t>deepakgilkarwar@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9000585824</t>
   </si>
   <si>
+    <t>Ganesh P</t>
+  </si>
+  <si>
+    <t>ganesh_p1003@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9731304127</t>
   </si>
   <si>
+    <t>Gopi Tedlapally</t>
+  </si>
+  <si>
+    <t>gopi_tedlapally@optum.com</t>
+  </si>
+  <si>
     <t>415-866-9351</t>
   </si>
   <si>
+    <t>Ishwarya Salibindla</t>
+  </si>
+  <si>
+    <t>salibindla_ishwarya@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9505609173</t>
   </si>
   <si>
+    <t>Kalyan K Dey</t>
+  </si>
+  <si>
+    <t>kalyan.dey@optum.com</t>
+  </si>
+  <si>
     <t>312-804-8062</t>
   </si>
   <si>
+    <t>Madhu Reddy</t>
+  </si>
+  <si>
+    <t>madhu_reddy1@optum.com</t>
+  </si>
+  <si>
     <t>425-785-7065</t>
   </si>
   <si>
+    <t>Manikanta Jitender Reddy Nallamilli</t>
+  </si>
+  <si>
+    <t>manikanta.nallamilli@optum.com</t>
+  </si>
+  <si>
     <t>224-944-1539</t>
   </si>
   <si>
+    <t>Marc Paolo S Llorera</t>
+  </si>
+  <si>
+    <t>marcpaolo_llorera@optum.com</t>
+  </si>
+  <si>
     <t>011-63-9992279096</t>
   </si>
   <si>
     <t>Philippines</t>
   </si>
   <si>
+    <t>Perwaize Ahmed</t>
+  </si>
+  <si>
+    <t>Perwaize.Ahmed@optum.com</t>
+  </si>
+  <si>
     <t>407-900-7652</t>
   </si>
   <si>
+    <t>Daggupati D Prasad</t>
+  </si>
+  <si>
+    <t>prasad_daggupati@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9849953299</t>
   </si>
   <si>
+    <t>Sabitha Nelakurthy</t>
+  </si>
+  <si>
+    <t>sabitha_nelakurthy@optum.com</t>
+  </si>
+  <si>
     <t>011-91-8792428081</t>
   </si>
   <si>
+    <t>Siva Sankar Devalla</t>
+  </si>
+  <si>
+    <t>sivasankar_devalla@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9000016089</t>
   </si>
   <si>
     <t>Venu</t>
   </si>
   <si>
+    <t>Venu Yamarapu</t>
+  </si>
+  <si>
+    <t>yamarapu_venu@optum.com</t>
+  </si>
+  <si>
     <t>011-91-9849909542</t>
   </si>
   <si>
     <t>Vijay</t>
+  </si>
+  <si>
+    <t>Vijay Pothula</t>
+  </si>
+  <si>
+    <t>Vijay.Pothula@optum.com</t>
   </si>
   <si>
     <t>630-452-4894</t>
@@ -271,7 +367,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +390,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -369,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -419,6 +521,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2708,205 +2811,315 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" t="str">
+        <f>_xlfn.TEXTBEFORE(B2, " ", 1)</f>
+        <v>Abhishek</v>
+      </c>
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="3" spans="1:5" ht="15">
+      <c r="A3" t="str">
+        <f>_xlfn.TEXTBEFORE(B3, " ", 1)</f>
+        <v>Avinash</v>
+      </c>
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" t="str">
+        <f>_xlfn.TEXTBEFORE(B4, " ", 1)</f>
+        <v>Deepak</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" t="str">
+        <f>_xlfn.TEXTBEFORE(B5, " ", 1)</f>
+        <v>Ganesh</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" t="str">
+        <f>_xlfn.TEXTBEFORE(B6, " ", 1)</f>
+        <v>Gopi</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" t="str">
+        <f>_xlfn.TEXTBEFORE(B7, " ", 1)</f>
+        <v>Ishwarya</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" t="str">
+        <f>_xlfn.TEXTBEFORE(B8, " ", 1)</f>
+        <v>Kalyan</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15">
+      <c r="A9" t="str">
+        <f>_xlfn.TEXTBEFORE(B9, " ", 1)</f>
+        <v>Madhu</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    <row r="14" spans="1:5" ht="15">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2" t="s">
+    <row r="15" spans="1:5" ht="15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="2" t="s">
+    <row r="16" spans="1:5" ht="15">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>57</v>
       </c>
     </row>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:C17">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="B2:C3 B5:C11 B13:C17 D2:E17">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
